--- a/251211/NMDAR_Seizures.xlsx
+++ b/251211/NMDAR_Seizures.xlsx
@@ -383,11 +383,11 @@
         </is>
       </c>
       <c r="B2">
-        <v>0.9874000000000001</v>
+        <v>0.8809</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.9693 – 1.0057</t>
+          <t>0.7321 – 1.0587</t>
         </is>
       </c>
       <c r="D2">
@@ -401,11 +401,11 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.9958</v>
+        <v>0.9586</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.9787 – 1.0132</t>
+          <t>0.8066 – 1.1406</t>
         </is>
       </c>
       <c r="D3">
@@ -419,11 +419,11 @@
         </is>
       </c>
       <c r="B4">
-        <v>1.0023</v>
+        <v>1.0235</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.9862 – 1.0191</t>
+          <t>0.87 – 1.2079</t>
         </is>
       </c>
       <c r="D4">
@@ -437,11 +437,11 @@
         </is>
       </c>
       <c r="B5">
-        <v>1.0056</v>
+        <v>1.0577</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.99 – 1.0218</t>
+          <t>0.9044 – 1.2406</t>
         </is>
       </c>
       <c r="D5">
@@ -455,11 +455,11 @@
         </is>
       </c>
       <c r="B6">
-        <v>0.86</v>
+        <v>0.985</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.1913 – 3.984</t>
+          <t>0.8475 – 1.1482</t>
         </is>
       </c>
       <c r="D6">
@@ -473,11 +473,11 @@
         </is>
       </c>
       <c r="B7">
-        <v>0.7224</v>
+        <v>0.968</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.1872 – 2.8487</t>
+          <t>0.8457 – 1.1104</t>
         </is>
       </c>
       <c r="D7">
@@ -491,11 +491,11 @@
         </is>
       </c>
       <c r="B8">
-        <v>1.2689</v>
+        <v>1.0241</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.3424 – 4.9038</t>
+          <t>0.8984 – 1.1723</t>
         </is>
       </c>
       <c r="D8">
@@ -509,11 +509,11 @@
         </is>
       </c>
       <c r="B9">
-        <v>1.2554</v>
+        <v>1.023</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.3506 – 4.6736</t>
+          <t>0.9005 – 1.1667</t>
         </is>
       </c>
       <c r="D9">
@@ -527,11 +527,11 @@
         </is>
       </c>
       <c r="B10">
-        <v>0.9689</v>
+        <v>0.7291</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.9487 – 0.989</t>
+          <t>0.5908 – 0.8954</t>
         </is>
       </c>
       <c r="D10">
@@ -545,11 +545,11 @@
         </is>
       </c>
       <c r="B11">
-        <v>0.9739</v>
+        <v>0.7675</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.9551 – 0.9927</t>
+          <t>0.6317 – 0.9296</t>
         </is>
       </c>
       <c r="D11">
@@ -563,11 +563,11 @@
         </is>
       </c>
       <c r="B12">
-        <v>0.9821</v>
+        <v>0.8349</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.9638 – 1.0006</t>
+          <t>0.6919 – 1.0058</t>
         </is>
       </c>
       <c r="D12">
@@ -581,11 +581,11 @@
         </is>
       </c>
       <c r="B13">
-        <v>0.9878</v>
+        <v>0.8844</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.9704 – 1.0055</t>
+          <t>0.7402 – 1.0566</t>
         </is>
       </c>
       <c r="D13">
@@ -599,11 +599,11 @@
         </is>
       </c>
       <c r="B14">
-        <v>0.9983</v>
+        <v>0.983</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.9833 – 1.0137</t>
+          <t>0.8453 – 1.1453</t>
         </is>
       </c>
       <c r="D14">
@@ -617,11 +617,11 @@
         </is>
       </c>
       <c r="B15">
-        <v>1.0086</v>
+        <v>1.0889</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.9917 – 1.026</t>
+          <t>0.9204 – 1.293</t>
         </is>
       </c>
       <c r="D15">
@@ -635,11 +635,11 @@
         </is>
       </c>
       <c r="B16">
-        <v>1.0061</v>
+        <v>1.0625</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.9906 – 1.0221</t>
+          <t>0.9102 – 1.2447</t>
         </is>
       </c>
       <c r="D16">
@@ -653,11 +653,11 @@
         </is>
       </c>
       <c r="B17">
-        <v>1.0034</v>
+        <v>1.0343</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.9881 – 1.0192</t>
+          <t>0.8876 – 1.2095</t>
         </is>
       </c>
       <c r="D17">
@@ -671,11 +671,11 @@
         </is>
       </c>
       <c r="B18">
-        <v>0.9882</v>
+        <v>0.8881</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.9728 – 1.0038</t>
+          <t>0.759 – 1.0382</t>
         </is>
       </c>
       <c r="D18">
@@ -689,11 +689,11 @@
         </is>
       </c>
       <c r="B19">
-        <v>0.9959</v>
+        <v>0.9601</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.9815 – 1.0107</t>
+          <t>0.83 – 1.112</t>
         </is>
       </c>
       <c r="D19">
@@ -707,11 +707,11 @@
         </is>
       </c>
       <c r="B20">
-        <v>1.0011</v>
+        <v>1.0115</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.9869 – 1.0158</t>
+          <t>0.8769 – 1.1698</t>
         </is>
       </c>
       <c r="D20">
@@ -725,11 +725,11 @@
         </is>
       </c>
       <c r="B21">
-        <v>1.0055</v>
+        <v>1.0562</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.9918 – 1.0196</t>
+          <t>0.9211 – 1.2147</t>
         </is>
       </c>
       <c r="D21">
@@ -743,11 +743,11 @@
         </is>
       </c>
       <c r="B22">
-        <v>0.9858</v>
+        <v>0.867</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.9635 – 1.0086</t>
+          <t>0.6895 – 1.0896</t>
         </is>
       </c>
       <c r="D22">
@@ -761,11 +761,11 @@
         </is>
       </c>
       <c r="B23">
-        <v>0.9945000000000001</v>
+        <v>0.9466</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.9736 – 1.0161</t>
+          <t>0.7649 – 1.1734</t>
         </is>
       </c>
       <c r="D23">
@@ -779,11 +779,11 @@
         </is>
       </c>
       <c r="B24">
-        <v>1.0033</v>
+        <v>1.0333</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.9838 – 1.0236</t>
+          <t>0.8495 – 1.263</t>
         </is>
       </c>
       <c r="D24">
@@ -797,11 +797,11 @@
         </is>
       </c>
       <c r="B25">
-        <v>1.008</v>
+        <v>1.0825</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.989 – 1.0278</t>
+          <t>0.8951 – 1.3155</t>
         </is>
       </c>
       <c r="D25">
@@ -815,11 +815,11 @@
         </is>
       </c>
       <c r="B26">
-        <v>0.9886</v>
+        <v>0.8915999999999999</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>0.9732 – 1.0041</t>
+          <t>0.7623 – 1.0417</t>
         </is>
       </c>
       <c r="D26">
@@ -833,11 +833,11 @@
         </is>
       </c>
       <c r="B27">
-        <v>0.9963</v>
+        <v>0.9635</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>0.9819 – 1.011</t>
+          <t>0.8333 – 1.1155</t>
         </is>
       </c>
       <c r="D27">
@@ -851,11 +851,11 @@
         </is>
       </c>
       <c r="B28">
-        <v>1.0013</v>
+        <v>1.0135</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>0.9872 – 1.016</t>
+          <t>0.8791 – 1.1715</t>
         </is>
       </c>
       <c r="D28">
@@ -869,11 +869,11 @@
         </is>
       </c>
       <c r="B29">
-        <v>1.005</v>
+        <v>1.0514</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>0.9914 – 1.0192</t>
+          <t>0.9172 – 1.2089</t>
         </is>
       </c>
       <c r="D29">
